--- a/เอกสารและรายชื่อคณะสีแสด_ปี69/แยกฝ่าย/พร็อพ/รายชื่อฝ่ายพร็อพ_คณะสีแสด_ปี69.xlsx
+++ b/เอกสารและรายชื่อคณะสีแสด_ปี69/แยกฝ่าย/พร็อพ/รายชื่อฝ่ายพร็อพ_คณะสีแสด_ปี69.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="77">
   <si>
     <t>🎨 รายชื่อสมาชิกฝ่ายพร็อพ — คณะสีแสด (สีบุษราคัม) ปี 2569</t>
   </si>
@@ -40,9 +40,6 @@
     <t>เบอร์โทรศัพท์</t>
   </si>
   <si>
-    <t>ม.4/14</t>
-  </si>
-  <si>
     <t>33221</t>
   </si>
   <si>
@@ -55,9 +52,6 @@
     <t>083-219-5152</t>
   </si>
   <si>
-    <t>ม.4/11</t>
-  </si>
-  <si>
     <t>35532</t>
   </si>
   <si>
@@ -76,9 +70,6 @@
     <t>082-906-9603</t>
   </si>
   <si>
-    <t>ม.3/1</t>
-  </si>
-  <si>
     <t>33617</t>
   </si>
   <si>
@@ -109,9 +100,6 @@
     <t>065-963-5206</t>
   </si>
   <si>
-    <t>ม.3/8</t>
-  </si>
-  <si>
     <t>33917</t>
   </si>
   <si>
@@ -121,9 +109,6 @@
     <t>095-358-9547</t>
   </si>
   <si>
-    <t>ม.3/10</t>
-  </si>
-  <si>
     <t>33995</t>
   </si>
   <si>
@@ -133,9 +118,6 @@
     <t>080-137-4426</t>
   </si>
   <si>
-    <t>ม.2/3</t>
-  </si>
-  <si>
     <t>34373</t>
   </si>
   <si>
@@ -145,9 +127,6 @@
     <t>082-594-4531</t>
   </si>
   <si>
-    <t>ม.3/3</t>
-  </si>
-  <si>
     <t>33719</t>
   </si>
   <si>
@@ -157,9 +136,6 @@
     <t>096-294-5586</t>
   </si>
   <si>
-    <t>ม.3/11</t>
-  </si>
-  <si>
     <t>34019</t>
   </si>
   <si>
@@ -169,9 +145,6 @@
     <t>098-951-4742</t>
   </si>
   <si>
-    <t>ม.3/9</t>
-  </si>
-  <si>
     <t>33965</t>
   </si>
   <si>
@@ -181,9 +154,6 @@
     <t>065-975-1810</t>
   </si>
   <si>
-    <t>ม.2/6</t>
-  </si>
-  <si>
     <t>34505</t>
   </si>
   <si>
@@ -202,9 +172,6 @@
     <t>099-272-6458</t>
   </si>
   <si>
-    <t>ม.3/5</t>
-  </si>
-  <si>
     <t>33815</t>
   </si>
   <si>
@@ -232,9 +199,6 @@
     <t>063-019-1154</t>
   </si>
   <si>
-    <t>ม.3/4</t>
-  </si>
-  <si>
     <t>33755</t>
   </si>
   <si>
@@ -253,9 +217,6 @@
     <t>083-097-3619</t>
   </si>
   <si>
-    <t>ม.3/2</t>
-  </si>
-  <si>
     <t>34862</t>
   </si>
   <si>
@@ -268,7 +229,7 @@
     <t>33683</t>
   </si>
   <si>
-    <t>นางสาวนวยนิน</t>
+    <t>นางสาวนวยนิน -</t>
   </si>
   <si>
     <t>083-097-3532</t>
@@ -811,506 +772,462 @@
       <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="B4" s="4"/>
       <c r="C4" s="4">
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="B5" s="6"/>
       <c r="C5" s="6">
         <v>29</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="B6" s="4"/>
       <c r="C6" s="4">
         <v>23</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>4</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="B7" s="6"/>
       <c r="C7" s="6">
         <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="B8" s="4"/>
       <c r="C8" s="4">
         <v>40</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>6</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="B9" s="6"/>
       <c r="C9" s="6">
         <v>21</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="B10" s="4"/>
       <c r="C10" s="4">
         <v>22</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>8</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>36</v>
-      </c>
+      <c r="B11" s="6"/>
       <c r="C11" s="6">
         <v>30</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="B12" s="4"/>
       <c r="C12" s="4">
         <v>28</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>10</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="B13" s="6"/>
       <c r="C13" s="6">
         <v>27</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="B14" s="4"/>
       <c r="C14" s="4">
         <v>24</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>12</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>52</v>
-      </c>
+      <c r="B15" s="6"/>
       <c r="C15" s="6">
         <v>30</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>56</v>
-      </c>
+      <c r="B16" s="4"/>
       <c r="C16" s="4">
         <v>39</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>14</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>40</v>
-      </c>
+      <c r="B17" s="6"/>
       <c r="C17" s="6">
         <v>34</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>63</v>
-      </c>
+      <c r="B18" s="4"/>
       <c r="C18" s="4">
         <v>40</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>16</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>63</v>
-      </c>
+      <c r="B19" s="6"/>
       <c r="C19" s="6">
         <v>42</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>63</v>
-      </c>
+      <c r="B20" s="4"/>
       <c r="C20" s="4">
         <v>34</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>18</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>73</v>
-      </c>
+      <c r="B21" s="6"/>
       <c r="C21" s="6">
         <v>22</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>73</v>
-      </c>
+      <c r="B22" s="4"/>
       <c r="C22" s="4">
         <v>28</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>20</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>80</v>
-      </c>
+      <c r="B23" s="6"/>
       <c r="C23" s="6">
         <v>40</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>80</v>
-      </c>
+      <c r="B24" s="4"/>
       <c r="C24" s="4">
         <v>26</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>22</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>80</v>
-      </c>
+      <c r="B25" s="6"/>
       <c r="C25" s="6">
         <v>38</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
